--- a/South_Bend_Master_Event_Sources.xlsx
+++ b/South_Bend_Master_Event_Sources.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -593,6 +593,21 @@
           <t>Recommended Priority</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alternate URL Candidate 1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Alternate URL Candidate 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Audit Status</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -625,6 +640,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -657,6 +677,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -689,6 +714,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -721,6 +751,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -753,6 +788,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -785,6 +825,16 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://palaisroyale.org/contact</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -817,6 +867,16 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.pigeonhenpottery.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -849,6 +909,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -881,6 +946,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://sbct.org/shows</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://ci.ovationtix.com/35243</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -913,6 +993,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -945,6 +1030,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://southbendart.org/all-events/</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://southbendart.org</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -977,6 +1077,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/calendar</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/events</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1009,6 +1124,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/special-events/</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/programs-events/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
@@ -1041,6 +1171,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1073,6 +1208,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
@@ -1105,6 +1245,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://wellfieldgardens.org/calendar</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.wellfieldgardens.org/calendar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1137,6 +1292,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
@@ -1169,6 +1329,16 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>http://chicoryeventcenter.com</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1201,6 +1371,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
@@ -1233,6 +1408,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1265,6 +1445,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
@@ -1297,6 +1482,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1329,6 +1519,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/calendar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/community/calendar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -1361,6 +1566,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1393,6 +1603,16 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.sunkingbrewing.com/private-events</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
@@ -1425,6 +1645,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -1457,6 +1682,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.wvpe.org/schedule</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.wvpe.org/all-shows</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -1489,6 +1729,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://barlouie.com/bar-louie-events/</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://barlouie.com/group-events/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -1521,6 +1776,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
@@ -1553,6 +1813,16 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.corbysirishpub.com/calendar--special-events.html</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -1585,6 +1855,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
@@ -1617,6 +1892,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://fourwindscasino.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://reservations2.fourwindscasino.com/ReservationCalendar.action</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -1649,6 +1939,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
@@ -1681,6 +1976,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -1713,6 +2013,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
@@ -1745,6 +2050,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -1777,6 +2087,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
@@ -1809,6 +2124,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -1841,6 +2161,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
@@ -1873,6 +2198,16 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://thegeneraldeli.com/general-events</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -1905,6 +2240,16 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.kirkwoodcollection.com/hideaway/events-room-blocks/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -1937,6 +2282,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -1969,6 +2319,11 @@
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
@@ -2001,6 +2356,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/calendar</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/events</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -2033,6 +2403,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/fire-ems/fire-prevention-bureau/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
@@ -2065,6 +2450,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.potawatomizoo.org/events</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://potawatomizoo.org/events/category/education-events/list/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -2097,6 +2497,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/schedule</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/milb/schedule</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
@@ -2129,6 +2544,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/shows</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -2161,6 +2591,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/calendar</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/518/Programs-Events</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -2193,6 +2638,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -2225,6 +2675,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
@@ -2257,6 +2722,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>http://micommunityfinancials.michigan.gov/#!/dashboard/CITY/2657760?lat=41.83453900000001&amp;lng=-86.24785099999997&amp;zoom=10&amp;showSidebar=yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.nilesmi.org/document_center/department/Clerk/SPECIAL EVENT APPLICATION - fillable.pdf</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -2289,6 +2769,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://southbendin.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
@@ -2321,6 +2816,21 @@
           <t>High (Top Target)</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/events</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/schedule</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -2353,6 +2863,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
@@ -2385,6 +2910,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -2417,6 +2947,21 @@
           <t>High (Top Target)</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
@@ -2449,6 +2994,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -2481,6 +3041,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.elkhartindiana.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
@@ -2513,6 +3088,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://myepl.org/calendar</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://myepl.org/community/calendar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -2545,6 +3135,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/events</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/list-of-events-programs</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
@@ -2577,6 +3182,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar/</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -2609,6 +3229,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
@@ -2641,6 +3266,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -2673,6 +3303,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
@@ -2705,6 +3340,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -2737,6 +3387,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
@@ -2769,6 +3424,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -2801,6 +3461,21 @@
           <t>High (Top Target)</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/calendar</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/events</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
@@ -2833,6 +3508,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
@@ -2865,6 +3545,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;eventType=inPerson&amp;sortField=DATETIME&amp;location=us--mi--Saint+Joseph</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/books-banter-a-book-club-for-women/events/316306457/?eventOrigin=home_logged_out_near_location</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
@@ -2897,6 +3592,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://promotix.com/event-creators</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.promotix.com/event-discovery/l/new</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -2929,6 +3639,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
@@ -2961,6 +3676,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/community/calendar</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
@@ -2993,6 +3723,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/events</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/event-calendar</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
@@ -3025,6 +3770,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/baseball/schedule/</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/mbball/schedule/</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -3057,6 +3817,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://dpactickets.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
@@ -3089,6 +3864,21 @@
           <t>High (Top Target)</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/submit-an-event</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -3121,6 +3911,21 @@
           <t>High</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/2026/10/31/halloweenfest/</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/calendar/featured/</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
@@ -3153,6 +3958,21 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/academics/resources/academic-calendar</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/spiritual-life/calendar</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -3185,6 +4005,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -3217,6 +4052,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -3249,6 +4089,21 @@
           <t>High (Top Target)</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/events</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/schedule</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
@@ -3281,6 +4136,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/events</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/schedule</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -3313,6 +4183,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/events</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
@@ -3345,6 +4230,21 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar.html</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -3375,6 +4275,11 @@
       <c r="F91" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
         </is>
       </c>
     </row>

--- a/South_Bend_Master_Event_Sources.xlsx
+++ b/South_Bend_Master_Event_Sources.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -837,128 +837,128 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Palais Royale (South Bend) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://palaisroyale.org/contact</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Big band galas, ballroom dance nights, holiday expos</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://palaisroyale.org/contact</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Pigeon &amp; The Hen Pottery</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>https://www.pigeonhenpottery.com</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Paint-your-own pottery nights, clay wheel classes, adult BYOB pottery, seasonal workshops</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Low (Static HTML)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.pigeonhenpottery.com/event-calendar</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Discovered 1 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>River Park Center / Nectar Coffee House</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/NectarCoffeeHouse</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Acoustic showcases, community galas, open mic poetry, indie pop-ups</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>High (Playwright/Social)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Arts, Culture &amp; Community</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>South Bend Civic Theatre</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>https://sbct.org</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Local theatrical plays, musicals, comedy workshops, improv shows</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pigeon &amp; The Hen Pottery (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.pigeonhenpottery.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Paint-your-own pottery nights, clay wheel classes, adult BYOB pottery, seasonal workshops</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://sbct.org/shows</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://ci.ovationtix.com/35243</t>
+          <t>https://www.pigeonhenpottery.com/event-calendar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Discovered 3 Candidates</t>
+          <t>Discovered 1 Candidates</t>
         </is>
       </c>
     </row>
@@ -970,27 +970,27 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>South Bend Dance Center &amp; Salsa SB</t>
+          <t>River Park Center / Nectar Coffee House</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>https://salsasouthbend.com</t>
+          <t>https://www.facebook.com/NectarCoffeeHouse</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Social salsa/bachata dance nights, beginner dance lessons, Latin dance socials</t>
+          <t>Acoustic showcases, community galas, open mic poetry, indie pop-ups</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Disabled - Domain Dead</t>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>South Bend Museum of Art (SBMA)</t>
+          <t>South Bend Civic Theatre</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://southbendart.org/events/</t>
+          <t>https://sbct.org</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Art openings, evening socials, studio workshops</t>
+          <t>Local theatrical plays, musicals, comedy workshops, improv shows</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1025,66 +1025,66 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://southbendart.org/all-events/</t>
+          <t>https://sbct.org/shows</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://southbendart.org</t>
+          <t>https://ci.ovationtix.com/35243</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Discovered 4 Candidates</t>
+          <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>South Bend Symphony Orchestra (SBSO)</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>https://southbendsymphony.org</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Symphony concerts, outdoor pops concerts, chamber music</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>South Bend Civic Theatre (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://sbct.org/shows</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Local theatrical plays, musicals, comedy workshops, improv shows</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://southbendsymphony.org/calendar</t>
+          <t>https://sbct.org/shows</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://southbendsymphony.org/events</t>
+          <t>https://ci.ovationtix.com/35243</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1094,49 +1094,49 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>St. Joseph County Public Library (SJCPL)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>https://sjcpl.org/events/</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Author talks, board game clubs, maker workshops, film screenings</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Low (LibCal API/HTML)</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>South Bend Civic Theatre (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://ci.ovationtix.com/35243</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Local theatrical plays, musicals, comedy workshops, improv shows</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://sjcpl.org/special-events/</t>
+          <t>https://sbct.org/shows</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://sjcpl.org/programs-events/</t>
+          <t>https://ci.ovationtix.com/35243</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Discovered 4 Candidates</t>
+          <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
@@ -1148,22 +1148,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>The Bendix Arena / Century Center Complex</t>
+          <t>South Bend Dance Center &amp; Salsa SB</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>https://bendixarena.com</t>
+          <t>https://salsasouthbend.com</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Esports tournaments, anime conventions, comic expos, roller derby matches</t>
+          <t>Social salsa/bachata dance nights, beginner dance lessons, Latin dance socials</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Low-Medium</t>
+          <t>Low (Static HTML)</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>The History Museum &amp; Studebaker Center</t>
+          <t>South Bend Museum of Art (SBMA)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://www.historymuseumsb.org/events/</t>
+          <t>https://southbendart.org/events/</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Mystery at the Mansion nights, outdoor car shows, history talks</t>
+          <t>Art openings, evening socials, studio workshops</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1203,56 +1203,66 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://southbendart.org/all-events/</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://southbendart.org</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Wellfield Botanic Gardens (Elkhart - 25m away)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>https://wellfieldgardens.org/events/</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Groovin' in the Gardens concerts, Winter Wonderland lights, wine walks</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>South Bend Museum of Art (SBMA) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://southbendart.org/all-events/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Art openings, evening socials, studio workshops</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://wellfieldgardens.org/calendar</t>
+          <t>https://southbendart.org/all-events/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.wellfieldgardens.org/calendar</t>
+          <t>https://southbendart.org</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1262,61 +1272,71 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Breweries &amp; Taprooms</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Bare Hands Brewery (Granger)</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>https://www.barehandsbrewery.com/events</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Beer festivals, food truck rallies, outdoor summer music</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>South Bend Museum of Art (SBMA) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://southbendart.org</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Art openings, evening socials, studio workshops</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://southbendart.org/all-events/</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://southbendart.org</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Breweries &amp; Taprooms</t>
+          <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Chicory Cafe &amp; Event Center (Mishawaka)</t>
+          <t>South Bend Symphony Orchestra (SBSO)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>https://chicorycafe.net/events/</t>
+          <t>https://southbendsymphony.org</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>BLAMMOWEEN, live acoustic sets, salsa nights, member mixers</t>
+          <t>Symphony concerts, outdoor pops concerts, chamber music</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1324,120 +1344,145 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>http://chicoryeventcenter.com</t>
+          <t>https://southbendsymphony.org/calendar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/events</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Discovered 1 Candidates</t>
+          <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Breweries &amp; Taprooms</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Crooked Ewe Brewery &amp; Ale House</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>https://crookedewe.com/events/</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Taproom release parties, patio live music, community dinners</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>South Bend Symphony Orchestra (SBSO) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/calendar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Symphony concerts, outdoor pops concerts, chamber music</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/calendar</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/events</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Breweries &amp; Taprooms</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Evil Checkmate / Local Craft Distilleries</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/EvilCheckmateBrewing</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Local craft release parties, board game socials, pub trivia</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>High (Playwright/Social)</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>South Bend Symphony Orchestra (SBSO) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/events</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Symphony concerts, outdoor pops concerts, chamber music</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/calendar</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://southbendsymphony.org/events</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Breweries &amp; Taprooms</t>
+          <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Evil Checkmate Brewery / Local Taprooms</t>
+          <t>St. Joseph County Public Library (SJCPL)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/EvilCheckmateBrewing</t>
+          <t>https://sjcpl.org/events/</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Cask nights, board game socials, pub trivia</t>
+          <t>Author talks, board game clubs, maker workshops, film screenings</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>High (Playwright/Social)</t>
+          <t>Low (LibCal API/HTML)</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1445,123 +1490,143 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/special-events/</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/programs-events/</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Breweries &amp; Taprooms</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Hop Station Craft Bar (Mishawaka)</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hopstationcraftbar.com</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Tap takeovers, craft beer tastings, community social nights</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>St. Joseph County Public Library (SJCPL) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/special-events/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Author talks, board game clubs, maker workshops, film screenings</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Low (LibCal API/HTML)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/special-events/</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/programs-events/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Breweries &amp; Taprooms</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Journeyman Distillery (Valparaiso/Three Oaks - 30m away)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>https://www.journeyman.com/events/</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Live music, artisan markets, comedy nights, whiskey tastings</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>St. Joseph County Public Library (SJCPL) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://sjcpl.org/programs-events/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Author talks, board game clubs, maker workshops, film screenings</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Low (LibCal API/HTML)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.journeyman.com/calendar</t>
+          <t>https://sjcpl.org/special-events/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.journeyman.com/community/calendar</t>
+          <t>https://sjcpl.org/programs-events/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Discovered 2 Candidates</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Breweries &amp; Taprooms</t>
+          <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Studebaker Brewing Co. / Tippecanoe</t>
+          <t>The Bendix Arena / Century Center Complex</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>https://tippecanoe.com/events</t>
+          <t>https://bendixarena.com</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Trivia nights, historic mansion tours, holiday murder mysteries</t>
+          <t>Esports tournaments, anime conventions, comic expos, roller derby matches</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Disabled - Domain Dead</t>
         </is>
@@ -1575,121 +1640,126 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Breweries &amp; Taprooms</t>
+          <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sun King Brewery Mishawaka</t>
+          <t>The History Museum &amp; Studebaker Center</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://www.sunkingbrewing.com/event-calendar</t>
+          <t>https://www.historymuseumsb.org/events/</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Trivia nights, cookie decorating, craft workshops, patio music</t>
+          <t>Mystery at the Mansion nights, outdoor car shows, history talks</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.sunkingbrewing.com/private-events</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Discovered 1 Candidates</t>
+          <t>Verified Original</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Media &amp; Calendars</t>
+          <t>Arts, Culture &amp; Community</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>South Bend Tribune Calendar</t>
+          <t>Wellfield Botanic Gardens (Elkhart - 25m away)</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>https://www.southbendtribune.com</t>
+          <t>https://wellfieldgardens.org/events/</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Civic parades, county fairs, community-wide festivals</t>
+          <t>Groovin' in the Gardens concerts, Winter Wonderland lights, wine walks</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Medium (Paywall/Dynamic)</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://wellfieldgardens.org/calendar</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.wellfieldgardens.org/calendar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Media &amp; Calendars</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>WVPE 88.1 Public Radio Calendar</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>https://www.wvpe.org/community-calendar</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Local arts, civic galas, theater productions, community cultural events</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wellfield Botanic Gardens (Elkhart - 25m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://wellfieldgardens.org/calendar</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Groovin' in the Gardens concerts, Winter Wonderland lights, wine walks</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.wvpe.org/schedule</t>
+          <t>https://wellfieldgardens.org/calendar</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.wvpe.org/all-shows</t>
+          <t>https://www.wellfieldgardens.org/calendar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1699,71 +1769,71 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Bar Louie (Heritage Square Granger)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>https://www.barlouie.com/locations/us/in/granger</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Late-night DJ sets, happy hour socials, music trivia</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Arts, Culture &amp; Community</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wellfield Botanic Gardens (Elkhart - 25m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.wellfieldgardens.org/calendar</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Groovin' in the Gardens concerts, Winter Wonderland lights, wine walks</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://barlouie.com/bar-louie-events/</t>
+          <t>https://wellfieldgardens.org/calendar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://barlouie.com/group-events/</t>
+          <t>https://www.wellfieldgardens.org/calendar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Discovered 2 Candidates</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Nightlife &amp; Social</t>
+          <t>Breweries &amp; Taprooms</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Chippewa Bowl / Strike Zone Entertainment</t>
+          <t>Bare Hands Brewery (Granger)</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://chippewabowl.com</t>
+          <t>https://www.barehandsbrewery.com/events</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Glow bowling nights, adult bowling leagues, arcade tournaments, live music</t>
+          <t>Beer festivals, food truck rallies, outdoor summer music</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1771,9 +1841,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1785,22 +1855,22 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Nightlife &amp; Social</t>
+          <t>Breweries &amp; Taprooms</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Corby's Irish Pub</t>
+          <t>Chicory Cafe &amp; Event Center (Mishawaka)</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>https://www.corbysirishpub.com</t>
+          <t>https://chicorycafe.net/events/</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Rudy film lore nights, game day tailgates, live local rock bands</t>
+          <t>BLAMMOWEEN, live acoustic sets, salsa nights, member mixers</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -1815,7 +1885,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.corbysirishpub.com/calendar--special-events.html</t>
+          <t>http://chicoryeventcenter.com</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1825,424 +1895,449 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Fiddler's Hearth</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>https://fiddlershearth.com</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Live traditional Irish sessions, open acoustic jams, pub trivia</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chicory Cafe &amp; Event Center (Mishawaka) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>http://chicoryeventcenter.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BLAMMOWEEN, live acoustic sets, salsa nights, member mixers</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>http://chicoryeventcenter.com</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Crooked Ewe Brewery &amp; Ale House</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>https://crookedewe.com/events/</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Taproom release parties, patio live music, community dinners</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Four Winds Casino South Bend Events</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>https://fourwindscasino.com/southbend/</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Live headliner concerts, Halloween/New Year bashes, casino night life</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Evil Checkmate / Local Craft Distilleries</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EvilCheckmateBrewing</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Local craft release parties, board game socials, pub trivia</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Evil Checkmate Brewery / Local Taprooms</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EvilCheckmateBrewing</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Cask nights, board game socials, pub trivia</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Hop Station Craft Bar (Mishawaka)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hopstationcraftbar.com</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Tap takeovers, craft beer tastings, community social nights</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Journeyman Distillery (Valparaiso/Three Oaks - 30m away)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/events/</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Live music, artisan markets, comedy nights, whiskey tastings</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://fourwindscasino.com/event-calendar</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://reservations2.fourwindscasino.com/ReservationCalendar.action</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Discovered 4 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Hammer &amp; Glass / Local Speakeasy Lounges</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hammerandglass.com</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Craft cocktail tastings, mixology classes, guest bartender socials</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/calendar</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/community/calendar</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Journeyman Distillery (Valparaiso/Three Oaks - 30m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/calendar</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Live music, artisan markets, comedy nights, whiskey tastings</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/calendar</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/community/calendar</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Journeyman Distillery (Valparaiso/Three Oaks - 30m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/community/calendar</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Live music, artisan markets, comedy nights, whiskey tastings</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/calendar</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.journeyman.com/community/calendar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Studebaker Brewing Co. / Tippecanoe</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>https://tippecanoe.com/events</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Trivia nights, historic mansion tours, holiday murder mysteries</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>Disabled - Domain Dead</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>International Fuse Bar &amp; Grill</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/InternationalFuseBarAndGrill</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Latin dance nights, singles mixers, DJ nights, theme parties</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>High (Playwright/Social)</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Kroc Center South Bend</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>https://www.mykroccenter.org</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Community sports tournaments, adult fitness challenges, swimming bashes, family nights</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Disabled - Domain Dead</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Peggs Downtown South Bend</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>https://peggsdowntown.com</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Brunch socials, mimosa bar events, patio live music</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Disabled - Domain Dead</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Social Cantina Mishawaka</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>https://socialcantina.com</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Taco Tuesday socials, outdoor patio DJ sets, margarita tastings</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Stockroom East</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>https://stockroomeast.com</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Pop-up music showcases, art pop-ups, social mixers, intimate concerts</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Sun King Brewery Mishawaka</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sunkingbrewing.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Trivia nights, cookie decorating, craft workshops, patio music</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>The Exchange Whiskey Bar (South Bend)</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>https://theexchangebar.com</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Whiskey masterclasses, speakeasy jazz nights, cocktail socials</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>The General Deli &amp; Cafe</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>https://thegeneraldeli.com/events/</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Indie acoustic showcases, game nights, poetry open mics, art gallery walks</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.sunkingbrewing.com/private-events</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Breweries &amp; Taprooms</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sun King Brewery Mishawaka (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.sunkingbrewing.com/private-events</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Trivia nights, cookie decorating, craft workshops, patio music</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://thegeneraldeli.com/general-events</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Discovered 1 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Nightlife &amp; Social</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>The Hideaway at the LaSalle</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>https://thehideawaysb.com</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Speakeasy cocktail nights, live jazz, themed bar crawls, singles mixers</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.kirkwoodcollection.com/hideaway/events-room-blocks/</t>
+          <t>https://www.sunkingbrewing.com/private-events</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2254,32 +2349,32 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Nightlife &amp; Social</t>
+          <t>Media &amp; Calendars</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Villa MacLaren / Outdoor Social Spaces</t>
+          <t>South Bend Tribune Calendar</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>https://villamaclaren.com</t>
+          <t>https://www.southbendtribune.com</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Boutique garden parties, wine socials, outdoor live music</t>
+          <t>Civic parades, county fairs, community-wide festivals</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium (Paywall/Dynamic)</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Disabled - Domain Dead</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2291,22 +2386,22 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Nightlife &amp; Social</t>
+          <t>Media &amp; Calendars</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Weiss' Gasthaus / German Pub Nights</t>
+          <t>WVPE 88.1 Public Radio Calendar</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://weissgasthaus.com/events/</t>
+          <t>https://www.wvpe.org/community-calendar</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Oktoberfest celebrations, German beer tastings, live accordion/folk bands</t>
+          <t>Local arts, civic galas, theater productions, community cultural events</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2316,101 +2411,111 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Disabled - Domain Dead</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.wvpe.org/schedule</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.wvpe.org/all-shows</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor, Parks &amp; Sports</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Howard Park Events</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>https://sbparksandrec.org</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Ice skating, summer concert series, night markets, fitness classes</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Low-Medium</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Media &amp; Calendars</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>WVPE 88.1 Public Radio Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.wvpe.org/schedule</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Local arts, civic galas, theater productions, community cultural events</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://sbparksandrec.org/calendar</t>
+          <t>https://www.wvpe.org/schedule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://sbparksandrec.org/events</t>
+          <t>https://www.wvpe.org/all-shows</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Discovered 3 Candidates</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Outdoor, Parks &amp; Sports</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Mishawaka Parks &amp; Rec Community Centers</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>https://mishawaka.in.gov/things-to-do/city-calendar/</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Battell Center craft markets, seasonal fun fairs, pickleball socials</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Media &amp; Calendars</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>WVPE 88.1 Public Radio Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.wvpe.org/all-shows</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Local arts, civic galas, theater productions, community cultural events</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+          <t>https://www.wvpe.org/schedule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://mishawaka.in.gov/government/departments/fire-ems/fire-prevention-bureau/</t>
+          <t>https://www.wvpe.org/all-shows</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2422,136 +2527,136 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Outdoor, Parks &amp; Sports</t>
+          <t>Nightlife &amp; Social</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Potawatomi Zoo</t>
+          <t>Bar Louie (Heritage Square Granger)</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>https://www.potawatomizoo.org</t>
+          <t>https://www.barlouie.com/locations/us/in/granger</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Beer in the Zoo (21+), Zoo Boo, seasonal evening fests</t>
+          <t>Late-night DJ sets, happy hour socials, music trivia</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.potawatomizoo.org/events</t>
+          <t>https://barlouie.com/bar-louie-events/</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://potawatomizoo.org/events/category/education-events/list/</t>
+          <t>https://barlouie.com/group-events/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Discovered 4 Candidates</t>
+          <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Outdoor, Parks &amp; Sports</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>South Bend Cubs / Four Winds Field</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>https://www.milb.com/south-bend</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Minor league baseball, fireworks nights, craft beer fests</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bar Louie (Heritage Square Granger) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://barlouie.com/bar-louie-events/</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Late-night DJ sets, happy hour socials, music trivia</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.milb.com/schedule</t>
+          <t>https://barlouie.com/bar-louie-events/</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.milb.com/milb/schedule</t>
+          <t>https://barlouie.com/group-events/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Discovered 4 Candidates</t>
+          <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor, Parks &amp; Sports</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>South Bend Venues Parks &amp; Arts (SBVPA)</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>https://sbvpa.org</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Leeper Park tennis, Pinhook Park socials, adult kickball leagues</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Low (Eventlink Integration)</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Bar Louie (Heritage Square Granger) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://barlouie.com/group-events/</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Late-night DJ sets, happy hour socials, music trivia</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://sbvpa.org/shows</t>
+          <t>https://barlouie.com/bar-louie-events/</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://sbvpa.org/things-to-do</t>
+          <t>https://barlouie.com/group-events/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2563,22 +2668,22 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Outdoor, Parks &amp; Sports</t>
+          <t>Nightlife &amp; Social</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>St. Joseph County Parks</t>
+          <t>Chippewa Bowl / Strike Zone Entertainment</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://www.sjcparks.org/calendar.aspx</t>
+          <t>https://chippewabowl.com</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Bitchikowski trail runs, night hikes, stargazing socials, paddle nights</t>
+          <t>Glow bowling nights, adult bowling leagues, arcade tournaments, live music</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2591,286 +2696,266 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.sjcparks.org/calendar</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>https://www.sjcparks.org/518/Programs-Events</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Discovered 4 Candidates</t>
+          <t>Verified Original</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Primary Aggregators</t>
+          <t>Nightlife &amp; Social</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Bandsintown (South Bend)</t>
+          <t>Corby's Irish Pub</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>https://www.bandsintown.com/c/south-bend-in</t>
+          <t>https://www.corbysirishpub.com</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Live music, touring bands, local concert schedules</t>
+          <t>Rudy film lore nights, game day tailgates, live local rock bands</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Medium (Dynamic Content)</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.corbysirishpub.com/calendar--special-events.html</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Corby's Irish Pub (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.corbysirishpub.com/calendar--special-events.html</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Rudy film lore nights, game day tailgates, live local rock bands</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.corbysirishpub.com/calendar--special-events.html</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Fiddler's Hearth</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>https://fiddlershearth.com</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Live traditional Irish sessions, open acoustic jams, pub trivia</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>City of Elkhart Events Calendar</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>https://www.visitelkhartcounty.com/events/</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Riverwalk concerts, Downtown Elkhart Jazz Fest, seasonal pop-ups</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.visitelkhartcounty.com/things-to-do</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>https://www.visitelkhartcounty.com/events/this-weekend/</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Discovered 3 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>City of Niles Events Calendar (MI - 15m away)</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>https://nilesmi.org</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Niles Apple Festival, Riverfront Park concerts, community block parties</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>http://micommunityfinancials.michigan.gov/#!/dashboard/CITY/2657760?lat=41.83453900000001&amp;lng=-86.24785099999997&amp;zoom=10&amp;showSidebar=yes</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>https://www.nilesmi.org/document_center/department/Clerk/SPECIAL EVENT APPLICATION - fillable.pdf</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Four Winds Casino South Bend Events</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>https://fourwindscasino.com/southbend/</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Live headliner concerts, Halloween/New Year bashes, casino night life</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://fourwindscasino.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://reservations2.fourwindscasino.com/ReservationCalendar.action</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>City of South Bend Official Calendar</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>https://southbendin.gov/events/</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>City council meetings, public hearings, street festivals, downtown parades</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Four Winds Casino South Bend Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://fourwindscasino.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Live headliner concerts, Halloween/New Year bashes, casino night life</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://southbendin.gov/things-to-do</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://sbvpa.org/things-to-do/</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Discovered 3 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Downtown South Bend (DTSB)</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>https://www.downtownsouthbend.com/calendar</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>First Fridays, block parties, street fairs, downtown bar crawls</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>High (Top Target)</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.downtownsouthbend.com/events</t>
+          <t>https://fourwindscasino.com/event-calendar</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.downtownsouthbend.com/schedule</t>
+          <t>https://reservations2.fourwindscasino.com/ReservationCalendar.action</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Discovered 2 Candidates</t>
+          <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Eventbrite (South Bend Region)</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>https://www.eventbrite.com/d/in--south-bend/events/</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Workshops, comedy shows, speed dating, bar crawls, indie concerts</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Medium (Dynamic / API)</t>
-        </is>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Four Winds Casino South Bend Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://reservations2.fourwindscasino.com/ReservationCalendar.action</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Live headliner concerts, Halloween/New Year bashes, casino night life</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/things-to-do</t>
+          <t>https://fourwindscasino.com/event-calendar</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.eventbrite.com/</t>
+          <t>https://reservations2.fourwindscasino.com/ReservationCalendar.action</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2880,1404 +2965,5709 @@
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Facebook Events (Local Tag)</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/events</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Grassroots events, DIY shows, pub trivia, pop-ups</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Hammer &amp; Glass / Local Speakeasy Lounges</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hammerandglass.com</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Craft cocktail tastings, mixology classes, guest bartender socials</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Disabled - Domain Dead</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>International Fuse Bar &amp; Grill</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InternationalFuseBarAndGrill</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Latin dance nights, singles mixers, DJ nights, theme parties</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>High (Playwright/Social)</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Primary Aggregators</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Visit South Bend Mishawaka</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>https://www.visitsouthbend.com/events/</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Regional festivals, community pop-ups, seasonal events, museum exhibits</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Low (Static HTML)</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>High (Top Target)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.visitsouthbend.com/things-to-do</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>https://www.visitsouthbend.com/events/this-weekend/</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Discovered 4 Candidates</t>
-        </is>
-      </c>
-    </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>City of Mishawaka Parks &amp; Rec</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
-        <is>
-          <t>https://mishawaka.in.gov/things-to-do/city-calendar/</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Battell Park summer concert series, Ironworks Plaza festivals, seasonal fests</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Kroc Center South Bend</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mykroccenter.org</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Community sports tournaments, adult fitness challenges, swimming bashes, family nights</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Disabled - Domain Dead</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Peggs Downtown South Bend</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>https://peggsdowntown.com</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>Brunch socials, mimosa bar events, patio live music</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Disabled - Domain Dead</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Social Cantina Mishawaka</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>https://socialcantina.com</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Taco Tuesday socials, outdoor patio DJ sets, margarita tastings</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Stockroom East</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>https://stockroomeast.com</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Pop-up music showcases, art pop-ups, social mixers, intimate concerts</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://mishawaka.in.gov/events</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Discovered 4 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Elkhart Civic &amp; Arts Events</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>https://www.elkhartindiana.org</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Wellfield Botanic Gardens evening events, Tolson Center festivals</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.elkhartindiana.org/things-to-do</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>https://www.visitelkhartcounty.com/events/</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Discovered 4 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Elkhart Public Library / Premier Arts</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>https://myepl.org/events/</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Community theater pop-ups, trivia nights, public book &amp; film socials</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://myepl.org/calendar</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>https://myepl.org/community/calendar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Discovered 3 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Fernwood Botanical Garden &amp; Nature Center (Niles, MI - 20m away)</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>https://www.fernwoodbotanical.org/calendar</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Luminaria walks, outdoor acoustic concerts, nature photography workshops, stargazing</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>The Exchange Whiskey Bar (South Bend)</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>https://theexchangebar.com</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Whiskey masterclasses, speakeasy jazz nights, cocktail socials</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>The General Deli &amp; Cafe</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>https://thegeneraldeli.com/events/</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Indie acoustic showcases, game nights, poetry open mics, art gallery walks</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.fernwoodbotanical.org/events</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>https://www.fernwoodbotanical.org/list-of-events-programs</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Discovered 4 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Good of Goshen / Downtown Goshen</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>https://downtowngoshen.org/events/</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>Goshen First Fridays, craft beer crawls, outdoor block parties</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://downtowngoshen.org/event-calendar</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>https://downtowngoshen.org/event-calendar/</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Discovered 4 Candidates</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Iron Shoe Distilling (Niles, MI - 15m away)</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>https://ironshoedistilling.com/events/</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Bourbon &amp; cocktail classes, patio acoustic music, burger &amp; spirits nights</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://thegeneraldeli.com/general-events</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>The General Deli &amp; Cafe (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://thegeneraldeli.com/general-events</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Indie acoustic showcases, game nights, poetry open mics, art gallery walks</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Verified Original</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>Regional Hubs</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Lehman's Orchard Brewery &amp; Winery (Niles, MI - 15m away)</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>https://lehmansorchard.com</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>Cider tastings, fruit picking festivals, orchard live music, wood-fired pizza nights</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://thegeneraldeli.com/general-events</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Verified Original</t>
+          <t>Discovered 1 Candidates</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>The Hideaway at the LaSalle</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>https://thehideawaysb.com</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Speakeasy cocktail nights, live jazz, themed bar crawls, singles mixers</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.kirkwoodcollection.com/hideaway/events-room-blocks/</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>The Hideaway at the LaSalle (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.kirkwoodcollection.com/hideaway/events-room-blocks/</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Speakeasy cocktail nights, live jazz, themed bar crawls, singles mixers</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.kirkwoodcollection.com/hideaway/events-room-blocks/</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Discovered 1 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Villa MacLaren / Outdoor Social Spaces</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>https://villamaclaren.com</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Boutique garden parties, wine socials, outdoor live music</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Disabled - Domain Dead</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Nightlife &amp; Social</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Weiss' Gasthaus / German Pub Nights</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>https://weissgasthaus.com/events/</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Oktoberfest celebrations, German beer tastings, live accordion/folk bands</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Disabled - Domain Dead</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Howard Park Events</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Ice skating, summer concert series, night markets, fitness classes</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/calendar</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/events</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Howard Park Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/calendar</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ice skating, summer concert series, night markets, fitness classes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/calendar</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/events</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Howard Park Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/events</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Ice skating, summer concert series, night markets, fitness classes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/calendar</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://sbparksandrec.org/events</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Mishawaka Parks &amp; Rec Community Centers</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do/city-calendar/</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Battell Center craft markets, seasonal fun fairs, pickleball socials</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/fire-ems/fire-prevention-bureau/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mishawaka Parks &amp; Rec Community Centers (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Battell Center craft markets, seasonal fun fairs, pickleball socials</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/fire-ems/fire-prevention-bureau/</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mishawaka Parks &amp; Rec Community Centers (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Battell Center craft markets, seasonal fun fairs, pickleball socials</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/fire-ems/fire-prevention-bureau/</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Potawatomi Zoo</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>https://www.potawatomizoo.org</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Beer in the Zoo (21+), Zoo Boo, seasonal evening fests</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.potawatomizoo.org/events</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://potawatomizoo.org/events/category/education-events/list/</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Potawatomi Zoo (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.potawatomizoo.org/events</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Beer in the Zoo (21+), Zoo Boo, seasonal evening fests</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.potawatomizoo.org/events</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://potawatomizoo.org/events/category/education-events/list/</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Potawatomi Zoo (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://potawatomizoo.org/events/category/education-events/list/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Beer in the Zoo (21+), Zoo Boo, seasonal evening fests</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.potawatomizoo.org/events</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://potawatomizoo.org/events/category/education-events/list/</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>South Bend Cubs / Four Winds Field</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/south-bend</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Minor league baseball, fireworks nights, craft beer fests</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/schedule</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/milb/schedule</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>South Bend Cubs / Four Winds Field (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/schedule</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Minor league baseball, fireworks nights, craft beer fests</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/schedule</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/milb/schedule</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>South Bend Cubs / Four Winds Field (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/milb/schedule</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Minor league baseball, fireworks nights, craft beer fests</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/schedule</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.milb.com/milb/schedule</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>South Bend Venues Parks &amp; Arts (SBVPA)</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Leeper Park tennis, Pinhook Park socials, adult kickball leagues</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Low (Eventlink Integration)</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/shows</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>South Bend Venues Parks &amp; Arts (SBVPA) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/shows</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Leeper Park tennis, Pinhook Park socials, adult kickball leagues</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Low (Eventlink Integration)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/shows</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>South Bend Venues Parks &amp; Arts (SBVPA) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Leeper Park tennis, Pinhook Park socials, adult kickball leagues</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Low (Eventlink Integration)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/shows</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>St. Joseph County Parks</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/calendar.aspx</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Bitchikowski trail runs, night hikes, stargazing socials, paddle nights</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/calendar</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/518/Programs-Events</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>St. Joseph County Parks (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/calendar</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Bitchikowski trail runs, night hikes, stargazing socials, paddle nights</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/calendar</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/518/Programs-Events</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Outdoor, Parks &amp; Sports</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>St. Joseph County Parks (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/518/Programs-Events</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Bitchikowski trail runs, night hikes, stargazing socials, paddle nights</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/calendar</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.sjcparks.org/518/Programs-Events</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Bandsintown (South Bend)</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bandsintown.com/c/south-bend-in</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Live music, touring bands, local concert schedules</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Medium (Dynamic Content)</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>City of Elkhart Events Calendar</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Riverwalk concerts, Downtown Elkhart Jazz Fest, seasonal pop-ups</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>City of Elkhart Events Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Riverwalk concerts, Downtown Elkhart Jazz Fest, seasonal pop-ups</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>City of Elkhart Events Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Riverwalk concerts, Downtown Elkhart Jazz Fest, seasonal pop-ups</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>City of Niles Events Calendar (MI - 15m away)</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>https://nilesmi.org</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Niles Apple Festival, Riverfront Park concerts, community block parties</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>http://micommunityfinancials.michigan.gov/#!/dashboard/CITY/2657760?lat=41.83453900000001&amp;lng=-86.24785099999997&amp;zoom=10&amp;showSidebar=yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.nilesmi.org/document_center/department/Clerk/SPECIAL EVENT APPLICATION - fillable.pdf</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>City of Niles Events Calendar (MI - 15m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>http://micommunityfinancials.michigan.gov/#!/dashboard/CITY/2657760?lat=41.83453900000001&amp;lng=-86.24785099999997&amp;zoom=10&amp;showSidebar=yes</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Niles Apple Festival, Riverfront Park concerts, community block parties</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>http://micommunityfinancials.michigan.gov/#!/dashboard/CITY/2657760?lat=41.83453900000001&amp;lng=-86.24785099999997&amp;zoom=10&amp;showSidebar=yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.nilesmi.org/document_center/department/Clerk/SPECIAL EVENT APPLICATION - fillable.pdf</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>City of Niles Events Calendar (MI - 15m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.nilesmi.org/document_center/department/Clerk/SPECIAL EVENT APPLICATION - fillable.pdf</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Niles Apple Festival, Riverfront Park concerts, community block parties</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>http://micommunityfinancials.michigan.gov/#!/dashboard/CITY/2657760?lat=41.83453900000001&amp;lng=-86.24785099999997&amp;zoom=10&amp;showSidebar=yes</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.nilesmi.org/document_center/department/Clerk/SPECIAL EVENT APPLICATION - fillable.pdf</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>City of South Bend Official Calendar</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>https://southbendin.gov/events/</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>City council meetings, public hearings, street festivals, downtown parades</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://southbendin.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do/</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>City of South Bend Official Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://southbendin.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>City council meetings, public hearings, street festivals, downtown parades</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://southbendin.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do/</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>City of South Bend Official Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do/</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>City council meetings, public hearings, street festivals, downtown parades</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://southbendin.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://sbvpa.org/things-to-do/</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Downtown South Bend (DTSB)</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/calendar</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>First Fridays, block parties, street fairs, downtown bar crawls</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/events</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/schedule</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Downtown South Bend (DTSB) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/events</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>First Fridays, block parties, street fairs, downtown bar crawls</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/events</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/schedule</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Downtown South Bend (DTSB) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/schedule</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>First Fridays, block parties, street fairs, downtown bar crawls</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/events</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.downtownsouthbend.com/schedule</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Eventbrite (South Bend Region)</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/in--south-bend/events/</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Workshops, comedy shows, speed dating, bar crawls, indie concerts</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Medium (Dynamic / API)</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Eventbrite (South Bend Region) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Workshops, comedy shows, speed dating, bar crawls, indie concerts</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Medium (Dynamic / API)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Eventbrite (South Bend Region) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Workshops, comedy shows, speed dating, bar crawls, indie concerts</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Medium (Dynamic / API)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Facebook Events (Local Tag)</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/events</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Grassroots events, DIY shows, pub trivia, pop-ups</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Visit South Bend Mishawaka</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/events/</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Regional festivals, community pop-ups, seasonal events, museum exhibits</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Visit South Bend Mishawaka (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Regional festivals, community pop-ups, seasonal events, museum exhibits</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Primary Aggregators</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Visit South Bend Mishawaka (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Regional festivals, community pop-ups, seasonal events, museum exhibits</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/things-to-do</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.visitsouthbend.com/events/this-weekend/</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
           <t>Regional Hubs</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>City of Mishawaka Parks &amp; Rec</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do/city-calendar/</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>Battell Park summer concert series, Ironworks Plaza festivals, seasonal fests</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>City of Mishawaka Parks &amp; Rec (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Battell Park summer concert series, Ironworks Plaza festivals, seasonal fests</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>City of Mishawaka Parks &amp; Rec (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Battell Park summer concert series, Ironworks Plaza festivals, seasonal fests</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/government/departments/police-department/</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Elkhart Civic &amp; Arts Events</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>https://www.elkhartindiana.org</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Wellfield Botanic Gardens evening events, Tolson Center festivals</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.elkhartindiana.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Elkhart Civic &amp; Arts Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.elkhartindiana.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Wellfield Botanic Gardens evening events, Tolson Center festivals</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.elkhartindiana.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Elkhart Civic &amp; Arts Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Wellfield Botanic Gardens evening events, Tolson Center festivals</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.elkhartindiana.org/things-to-do</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.visitelkhartcounty.com/events/</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Elkhart Public Library / Premier Arts</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>https://myepl.org/events/</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>Community theater pop-ups, trivia nights, public book &amp; film socials</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://myepl.org/calendar</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://myepl.org/community/calendar</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Elkhart Public Library / Premier Arts (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://myepl.org/calendar</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Community theater pop-ups, trivia nights, public book &amp; film socials</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://myepl.org/calendar</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://myepl.org/community/calendar</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Elkhart Public Library / Premier Arts (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://myepl.org/community/calendar</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Community theater pop-ups, trivia nights, public book &amp; film socials</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://myepl.org/calendar</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://myepl.org/community/calendar</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Fernwood Botanical Garden &amp; Nature Center (Niles, MI - 20m away)</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/calendar</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Luminaria walks, outdoor acoustic concerts, nature photography workshops, stargazing</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/events</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/list-of-events-programs</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Fernwood Botanical Garden &amp; Nature Center (Niles, MI - 20m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/events</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Luminaria walks, outdoor acoustic concerts, nature photography workshops, stargazing</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/events</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/list-of-events-programs</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fernwood Botanical Garden &amp; Nature Center (Niles, MI - 20m away) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/list-of-events-programs</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Luminaria walks, outdoor acoustic concerts, nature photography workshops, stargazing</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/events</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.fernwoodbotanical.org/list-of-events-programs</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>Good of Goshen / Downtown Goshen</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/events/</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>Goshen First Fridays, craft beer crawls, outdoor block parties</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar/</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Good of Goshen / Downtown Goshen (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Goshen First Fridays, craft beer crawls, outdoor block parties</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar/</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Good of Goshen / Downtown Goshen (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar/</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Goshen First Fridays, craft beer crawls, outdoor block parties</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://downtowngoshen.org/event-calendar/</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Iron Shoe Distilling (Niles, MI - 15m away)</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>https://ironshoedistilling.com/events/</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Bourbon &amp; cocktail classes, patio acoustic music, burger &amp; spirits nights</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>Lehman's Orchard Brewery &amp; Winery (Niles, MI - 15m away)</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>https://lehmansorchard.com</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>Cider tastings, fruit picking festivals, orchard live music, wood-fired pizza nights</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>McCoy Creek Trail &amp; Buchanan Art Center (Buchanan, MI - 20m away)</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>https://buchananartcenter.com</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Pottery workshops, artisan pop-up markets, summer outdoor concerts</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>Regional Hubs</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>Mishawaka Amphitheater / Beutter Park</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>https://mishawaka.in.gov</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>Outdoor movie nights, food truck festivals, riverwalk runs</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://mishawaka.in.gov/events</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>https://mishawaka.in.gov/things-to-do</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Regional Hubs</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Mishawaka Amphitheater / Beutter Park (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Outdoor movie nights, food truck festivals, riverwalk runs</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Mishawaka Amphitheater / Beutter Park (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Outdoor movie nights, food truck festivals, riverwalk runs</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/events</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://mishawaka.in.gov/things-to-do</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Regional Hubs</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>Rulli's Italian / Local Event Room (Mishawaka/Middlebury)</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>https://rullis.com</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>Wine pairing dinners, Italian cooking classes, community socials</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>Social Media &amp; Reddit</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>Downtown South Bend IG/FB</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>https://www.facebook.com/downtownsouthbend</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Pop-up food truck rallies, short-notice outdoor events</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>High (Playwright/Social)</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Social Media &amp; Reddit</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Downtown South Bend IG/FB (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Pop-up food truck rallies, short-notice outdoor events</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Social Media &amp; Reddit</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Downtown South Bend IG/FB (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/schedule</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Pop-up food truck rallies, short-notice outdoor events</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>Social Media &amp; Reddit</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>r/SouthBend Subreddit</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/SouthBend/</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>Weekly megathreads, DIY music, gaming nights, local meetups</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>Low (PRAW API / Reddit API)</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>High (Top Target)</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://www.reddit.com/calendar</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>https://www.reddit.com/events</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Social Media &amp; Reddit</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>r/SouthBend Subreddit (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/calendar</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Weekly megathreads, DIY music, gaming nights, local meetups</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Low (PRAW API / Reddit API)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/calendar</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/events</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Social Media &amp; Reddit</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>r/SouthBend Subreddit (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/events</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Weekly megathreads, DIY music, gaming nights, local meetups</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Low (PRAW API / Reddit API)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/calendar</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/events</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>Ticketing &amp; Meetup</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>Heritage Square Granger Events</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C139" s="8" t="inlineStr">
         <is>
           <t>https://shopheritagesquare.com/events/</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D139" s="8" t="inlineStr">
         <is>
           <t>Granger Farmers Market, summer wine walks, outdoor fitness socials</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>Ticketing &amp; Meetup</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>Meetup.com (South Bend Region)</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>https://www.meetup.com/find/us--in--south-bend/</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>Board game groups, outdoor hiking, tech meetups, social young adult groups</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Medium (Meetup API/HTML)</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F140" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>https://www.meetup.com/find/?source=EVENTS&amp;eventType=inPerson&amp;sortField=DATETIME&amp;location=us--mi--Saint+Joseph</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>https://www.meetup.com/books-banter-a-book-club-for-women/events/316306457/?eventOrigin=home_logged_out_near_location</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Ticketing &amp; Meetup</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Meetup.com (South Bend Region) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;eventType=inPerson&amp;sortField=DATETIME&amp;location=us--mi--Saint+Joseph</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Board game groups, outdoor hiking, tech meetups, social young adult groups</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Medium (Meetup API/HTML)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;eventType=inPerson&amp;sortField=DATETIME&amp;location=us--mi--Saint+Joseph</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/books-banter-a-book-club-for-women/events/316306457/?eventOrigin=home_logged_out_near_location</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Ticketing &amp; Meetup</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Meetup.com (South Bend Region) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/books-banter-a-book-club-for-women/events/316306457/?eventOrigin=home_logged_out_near_location</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Board game groups, outdoor hiking, tech meetups, social young adult groups</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Medium (Meetup API/HTML)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/find/?source=EVENTS&amp;eventType=inPerson&amp;sortField=DATETIME&amp;location=us--mi--Saint+Joseph</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/books-banter-a-book-club-for-women/events/316306457/?eventOrigin=home_logged_out_near_location</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>Ticketing &amp; Meetup</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>PromoTix (South Bend Region)</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C143" s="8" t="inlineStr">
         <is>
           <t>https://www.promotix.com/event-discovery/cities/south-bend-in/</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D143" s="8" t="inlineStr">
         <is>
           <t>Independent EDM/DJ nights, indie concerts, niche pop-up events</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>Low-Medium</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>https://promotix.com/event-creators</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>https://www.promotix.com/event-discovery/l/new</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Ticketing &amp; Meetup</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PromoTix (South Bend Region) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://promotix.com/event-creators</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Independent EDM/DJ nights, indie concerts, niche pop-up events</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://promotix.com/event-creators</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.promotix.com/event-discovery/l/new</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Ticketing &amp; Meetup</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PromoTix (South Bend Region) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.promotix.com/event-discovery/l/new</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Independent EDM/DJ nights, indie concerts, niche pop-up events</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://promotix.com/event-creators</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.promotix.com/event-discovery/l/new</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Ticketing &amp; Meetup</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>University Park Mall Community Events</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>https://www.simon.com/mall/university-park-mall/stream</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>Ski &amp; Snowboard Swap, seasonal expos, pop-up artisan fairs</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>Holy Cross College Events</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C147" s="8" t="inlineStr">
         <is>
           <t>https://www.hcc-nd.edu</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D147" s="8" t="inlineStr">
         <is>
           <t>Campus social gatherings, community events, athletic matches</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.hcc-nd.edu/calendar</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>https://www.hcc-nd.edu/community/calendar</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Holy Cross College Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Campus social gatherings, community events, athletic matches</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/community/calendar</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Holy Cross College Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/community/calendar</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Campus social gatherings, community events, athletic matches</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.hcc-nd.edu/community/calendar</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>IUSB Community Events Calendar</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>https://events.iu.edu#lw_cal</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>Local theater productions, music recitals, public talks, community workshops</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>Low (IU Events API/HTML)</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
         <is>
           <t>https://events.iu.edu/events</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>https://events.iu.edu/event-calendar</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>IUSB Community Events Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/events</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Local theater productions, music recitals, public talks, community workshops</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Low (IU Events API/HTML)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/events</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/event-calendar</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IUSB Community Events Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/event-calendar</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Local theater productions, music recitals, public talks, community workshops</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Low (IU Events API/HTML)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/events</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://events.iu.edu/event-calendar</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>Notre Dame Athletics Calendar</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t>https://fightingirish.com</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D153" s="8" t="inlineStr">
         <is>
           <t>Varsity matches, tailgate fests, open intramurals, fan festivals</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E153" s="7" t="inlineStr">
         <is>
           <t>Medium (Sidearm Sports)</t>
         </is>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F153" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://fightingirish.com/sports/baseball/schedule/</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>https://fightingirish.com/sports/mbball/schedule/</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Notre Dame Athletics Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/baseball/schedule/</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Varsity matches, tailgate fests, open intramurals, fan festivals</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Medium (Sidearm Sports)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/baseball/schedule/</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/mbball/schedule/</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Notre Dame Athletics Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/mbball/schedule/</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Varsity matches, tailgate fests, open intramurals, fan festivals</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Medium (Sidearm Sports)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/baseball/schedule/</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://fightingirish.com/sports/mbball/schedule/</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
         <is>
           <t>Notre Dame DeBartolo Performing Arts Center (DPAC)</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C156" s="5" t="inlineStr">
         <is>
           <t>https://performingarts.nd.edu/events/</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>Indie cinema, Shakespeare plays, visiting symphonies, student films</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F156" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://performingarts.nd.edu/calendar</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>https://dpactickets.nd.edu/events</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Notre Dame DeBartolo Performing Arts Center (DPAC) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Indie cinema, Shakespeare plays, visiting symphonies, student films</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://dpactickets.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Notre Dame DeBartolo Performing Arts Center (DPAC) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://dpactickets.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Indie cinema, Shakespeare plays, visiting symphonies, student films</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://dpactickets.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>Notre Dame Master Events Calendar</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C159" s="8" t="inlineStr">
         <is>
           <t>https://events.nd.edu</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D159" s="8" t="inlineStr">
         <is>
           <t>Campus-wide concerts, public lectures, sports tailgates, art exhibits, films</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E159" s="7" t="inlineStr">
         <is>
           <t>Low (Static HTML / RSS)</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F159" s="10" t="inlineStr">
         <is>
           <t>High (Top Target)</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://events.nd.edu/events</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>https://events.nd.edu/submit-an-event</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Notre Dame Master Events Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Campus-wide concerts, public lectures, sports tailgates, art exhibits, films</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Low (Static HTML / RSS)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/submit-an-event</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Notre Dame Master Events Calendar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/submit-an-event</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Campus-wide concerts, public lectures, sports tailgates, art exhibits, films</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Low (Static HTML / RSS)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://events.nd.edu/submit-an-event</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>Notre Dame Student Activities (SAO)</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
         <is>
           <t>https://sao.nd.edu/events/</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>Student concerts, campus trivia, seasonal bashes, outdoor festivals</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>Low-Medium</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F162" s="10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>https://sao.nd.edu/events/2026/10/31/halloweenfest/</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>https://sao.nd.edu/events/calendar/featured/</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>Discovered 4 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>University &amp; Campus</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Notre Dame Student Activities (SAO) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/2026/10/31/halloweenfest/</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Student concerts, campus trivia, seasonal bashes, outdoor festivals</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/2026/10/31/halloweenfest/</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/calendar/featured/</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Notre Dame Student Activities (SAO) (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/calendar/featured/</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Student concerts, campus trivia, seasonal bashes, outdoor festivals</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/2026/10/31/halloweenfest/</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://sao.nd.edu/events/calendar/featured/</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Discovered 4 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>Saint Mary's College Events</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C165" s="8" t="inlineStr">
         <is>
           <t>https://www.saintmarys.edu/events</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D165" s="8" t="inlineStr">
         <is>
           <t>Guest lectures, theatrical performances, dance recitals, art shows</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.saintmarys.edu/academics/resources/academic-calendar</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>https://www.saintmarys.edu/spiritual-life/calendar</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Saint Mary's College Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/academics/resources/academic-calendar</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Guest lectures, theatrical performances, dance recitals, art shows</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/academics/resources/academic-calendar</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/spiritual-life/calendar</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>University &amp; Campus</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Saint Mary's College Events (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/spiritual-life/calendar</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Guest lectures, theatrical performances, dance recitals, art shows</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/academics/resources/academic-calendar</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://www.saintmarys.edu/spiritual-life/calendar</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>DeBartolo Performing Arts Center</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>https://performingarts.nd.edu</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>Films, classical concerts, theater, campus-adjacent shows</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>Low-Medium</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://performingarts.nd.edu/calendar</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H168" t="inlineStr">
         <is>
           <t>https://performingarts.nd.edu/events</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I168" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>DeBartolo Performing Arts Center (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Films, classical concerts, theater, campus-adjacent shows</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>DeBartolo Performing Arts Center (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Films, classical concerts, theater, campus-adjacent shows</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/calendar</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://performingarts.nd.edu/events</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>IRONHAND Wine Bar</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C171" s="8" t="inlineStr">
         <is>
           <t>https://ironhandwinebar.com</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D171" s="8" t="inlineStr">
         <is>
           <t>Acoustic live music, wine tastings, social mixers</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>LangLab</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
         <is>
           <t>https://www.langlabsb.com</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>Indie concerts, art markets, community dinners, board game nights</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E172" s="4" t="inlineStr">
         <is>
           <t>Low (Static HTML)</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F172" s="10" t="inlineStr">
         <is>
           <t>High (Top Target)</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>https://www.langlabsb.com/events</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>https://www.langlabsb.com/schedule</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I172" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>LangLab (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/events</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Indie concerts, art markets, community dinners, board game nights</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/events</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/schedule</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>LangLab (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/schedule</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Indie concerts, art markets, community dinners, board game nights</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>High (Top Target)</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/events</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.langlabsb.com/schedule</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>Merrimans' Playhouse</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C175" s="8" t="inlineStr">
         <is>
           <t>https://merrimansplayhouse.org</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D175" s="8" t="inlineStr">
         <is>
           <t>Live jazz concerts, jam sessions, intimate listening room</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>Low (Static HTML)</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
         <is>
           <t>https://merrimansplayhouse.org/events</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>https://merrimansplayhouse.org/schedule</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I175" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Merrimans' Playhouse (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/events</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Live jazz concerts, jam sessions, intimate listening room</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/events</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/schedule</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Merrimans' Playhouse (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/schedule</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Live jazz concerts, jam sessions, intimate listening room</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/events</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://merrimansplayhouse.org/schedule</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>Morris Performing Arts Center</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>https://morriscenter.org</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>Broadway shows, touring comedy, orchestra, major headliners</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E178" s="4" t="inlineStr">
         <is>
           <t>Low-Medium</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
         <is>
           <t>https://morriscenter.org/events</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>https://morriscenter.org/upcoming-events</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>Discovered 3 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Morris Performing Arts Center (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/events</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Broadway shows, touring comedy, orchestra, major headliners</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/events</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Morris Performing Arts Center (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Broadway shows, touring comedy, orchestra, major headliners</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/events</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://morriscenter.org/upcoming-events</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Discovered 3 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>The Drop Comedy Club</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C181" s="8" t="inlineStr">
         <is>
           <t>https://thedropcomedyclub.com</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D181" s="8" t="inlineStr">
         <is>
           <t>Stand-up comedy, touring headliners, open mic nights</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>Low (Static HTML)</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://thedropcomedyclub.com/calendar</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>https://thedropcomedyclub.com/calendar.html</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I181" t="inlineStr">
         <is>
           <t>Discovered 2 Candidates</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>Venues &amp; Nightlife</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>The Drop Comedy Club (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Stand-up comedy, touring headliners, open mic nights</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar.html</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>The Drop Comedy Club (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar.html</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Stand-up comedy, touring headliners, open mic nights</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Low (Static HTML)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://thedropcomedyclub.com/calendar.html</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Discovered 2 Candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
         <is>
           <t>The Garage Arcade Bar</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
         <is>
           <t>https://www.facebook.com/TheGarageArcadeBar</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>Pinball/arcade tournaments, themed drink nights</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E184" s="4" t="inlineStr">
         <is>
           <t>High (Playwright/Social)</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>The Garage Arcade Bar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/event-calendar</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Pinball/arcade tournaments, themed drink nights</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Verified Original</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Venues &amp; Nightlife</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>The Garage Arcade Bar (Alt Endpoint)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/upcoming-events</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Pinball/arcade tournaments, themed drink nights</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>High (Playwright/Social)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
         <is>
           <t>Verified Original</t>
         </is>
